--- a/louvers/files/reference_xls/price_xls/aerofoil_af100.xlsx
+++ b/louvers/files/reference_xls/price_xls/aerofoil_af100.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7A3395-1316-4D4F-B204-2B3D70D05F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC60F11-71C3-2646-9F4D-654C7D32E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Price" sheetId="3" r:id="rId1"/>
@@ -735,10 +735,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1128,39 +1128,39 @@
       </c>
       <c r="B2" s="20">
         <f>C2/10.76391</f>
-        <v>753.90819878650052</v>
+        <v>829.29901866515058</v>
       </c>
       <c r="C2" s="21">
         <f>((1000/B8)*'Per m weight'!B3)*A8</f>
-        <v>8115</v>
+        <v>8926.5</v>
       </c>
       <c r="D2" s="22">
         <f>+A8*'Per m weight'!B3</f>
-        <v>811.5</v>
+        <v>892.65000000000009</v>
       </c>
       <c r="E2" s="32">
         <f>F2/10.76391</f>
-        <v>828.0679050177863</v>
+        <v>903.45872489643637</v>
       </c>
       <c r="F2" s="33">
         <f>C2+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B8))*'Coating Rate'!C1)</f>
-        <v>8913.2484034999998</v>
+        <v>9724.7484034999998</v>
       </c>
       <c r="G2" s="34">
         <f>+D2+((('Per m weight'!C3/25.4)*39.37008)*'Coating Rate'!C1)</f>
-        <v>891.32516220472439</v>
+        <v>972.47516220472448</v>
       </c>
       <c r="H2" s="44">
         <f>I2/10.76391</f>
-        <v>961.55537623410078</v>
+        <v>1036.9461961127508</v>
       </c>
       <c r="I2" s="45">
         <f>C2+(((('Per m weight'!C3*0.03937)*39.37)*(1000/B8))*0.7)</f>
-        <v>10350.095529799999</v>
+        <v>11161.595529799999</v>
       </c>
       <c r="J2" s="46">
         <f>+D2+((('Per m weight'!C3/25.4)*39.37008)*'Coating Rate'!C2)</f>
-        <v>1003.0803892913386</v>
+        <v>1084.2303892913387</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1169,39 +1169,39 @@
       </c>
       <c r="B3" s="23">
         <f>C3/10.76391</f>
-        <v>80.755970646354356</v>
+        <v>88.831567710989788</v>
       </c>
       <c r="C3" s="24">
         <f>((((1000/B8)*2)*50/1000)*'Per m weight'!B4)*A8</f>
-        <v>869.25</v>
+        <v>956.17500000000007</v>
       </c>
       <c r="D3" s="25">
         <f>CEILING(((A8*'Per m weight'!B4)*0.15),10)</f>
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E3" s="35">
         <f>F3/10.76391</f>
-        <v>90.115933568749654</v>
+        <v>98.191530633385099</v>
       </c>
       <c r="F3" s="36">
         <f>C3+(((('Per m weight'!C4*0.03937)*39.37)*((1000/B8)*2)*50/1000)*'Coating Rate'!C1)</f>
-        <v>969.9997985</v>
+        <v>1056.9247985000002</v>
       </c>
       <c r="G3" s="37">
         <f>+D3+((('Per m weight'!C4/25.4)*6)*'Coating Rate'!C1)</f>
-        <v>155.35433070866142</v>
+        <v>165.35433070866142</v>
       </c>
       <c r="H3" s="47">
         <f>I3/10.76391</f>
-        <v>106.9638668290612</v>
+        <v>115.03946389369663</v>
       </c>
       <c r="I3" s="48">
         <f>C3+(((('Per m weight'!C4*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*0.7)</f>
-        <v>1151.3494358</v>
+        <v>1238.2744358</v>
       </c>
       <c r="J3" s="49">
         <f>+D3+((('Per m weight'!C4/25.4)*6)*'Coating Rate'!C2)</f>
-        <v>176.85039370078741</v>
+        <v>186.85039370078741</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1210,39 +1210,39 @@
       </c>
       <c r="B4" s="23">
         <f>C4/10.76391</f>
-        <v>69.259219001273706</v>
+        <v>76.18514090140107</v>
       </c>
       <c r="C4" s="24">
         <f>((((1000/B8)*2)*50/1000)*'Per m weight'!B5)*A8</f>
-        <v>745.5</v>
+        <v>820.05</v>
       </c>
       <c r="D4" s="25">
         <f>+CEILING(((A8*'Per m weight'!B5)*0.15),10)</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E4" s="35">
         <f>F4/10.76391</f>
-        <v>73.507202173745426</v>
+        <v>80.43312407387279</v>
       </c>
       <c r="F4" s="36">
         <f>C4+(((('Per m weight'!C5*0.03937)*39.37)*((1000/B8)*2)*50/1000)*'Coating Rate'!C1)</f>
-        <v>791.22490855000001</v>
+        <v>865.77490854999996</v>
       </c>
       <c r="G4" s="37">
         <f>+D4+((('Per m weight'!C5/25.4)*6)*'Coating Rate'!C1)</f>
-        <v>126.96850393700788</v>
+        <v>136.96850393700788</v>
       </c>
       <c r="H4" s="47">
         <f>I4/10.76391</f>
-        <v>81.153571884194506</v>
+        <v>88.079493784321869</v>
       </c>
       <c r="I4" s="48">
         <f>C4+(((('Per m weight'!C5*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*0.7)</f>
-        <v>873.52974394</v>
+        <v>948.07974393999996</v>
       </c>
       <c r="J4" s="49">
         <f>+D4+((('Per m weight'!C5/25.4)*6)*'Coating Rate'!C2)</f>
-        <v>136.7244094488189</v>
+        <v>146.7244094488189</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="16" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1251,29 +1251,29 @@
       </c>
       <c r="B5" s="26">
         <f>CEILING((SUM(B2:B4)),10)</f>
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="C5" s="27">
         <f>CEILING((SUM(C2:C4)),10)</f>
-        <v>9730</v>
+        <v>10710</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="38">
         <f>+CEILING((SUM(E2:E4)),10)</f>
-        <v>1000</v>
+        <v>1090</v>
       </c>
       <c r="F5" s="39">
         <f>+CEILING((SUM(F2:F4)),10)</f>
-        <v>10680</v>
+        <v>11650</v>
       </c>
       <c r="G5" s="40"/>
       <c r="H5" s="50">
         <f t="shared" ref="H5:I5" si="0">+CEILING((SUM(H2:H4)),10)</f>
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="I5" s="51">
         <f t="shared" si="0"/>
-        <v>12380</v>
+        <v>13350</v>
       </c>
       <c r="J5" s="52"/>
     </row>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B8" s="15">
         <v>100</v>
@@ -1323,11 +1323,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
     </row>
     <row r="2" spans="1:7" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1399,19 +1399,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="58"/>
       <c r="C1" s="1">
         <v>0.25</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="1">
         <v>0.6</v>
       </c>
